--- a/unified-reports/backend-test-report.xlsx
+++ b/unified-reports/backend-test-report.xlsx
@@ -16,7 +16,7 @@
     <t>AgriNex Backend API Test Verification Report</t>
   </si>
   <si>
-    <t>Generated on: 11/8/2026, 10:50:45 am | Total Items: 300 | Status: 100% Passed / Stable</t>
+    <t>Generated on: 11/8/2026, 11:30:31 am | Total Items: 300 | Status: 100% Passed / Stable</t>
   </si>
   <si>
     <t>Test ID</t>
